--- a/branches/master/StructureDefinition-mii-pr-dokument-dokument.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-dokument-dokument.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T22:42:36+00:00</t>
+    <t>2026-09-12T22:48:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-dokument-dokument.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-dokument-dokument.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T22:48:46+00:00</t>
+    <t>2026-09-12T23:05:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-dokument-dokument.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-dokument-dokument.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T23:05:35+00:00</t>
+    <t>2026-09-13T05:04:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-dokument-dokument.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-dokument-dokument.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-13T05:04:18+00:00</t>
+    <t>2026-09-13T05:23:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-dokument-dokument.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-dokument-dokument.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-13T05:23:38+00:00</t>
+    <t>2026-09-13T05:43:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-dokument-dokument.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-dokument-dokument.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-13T05:43:21+00:00</t>
+    <t>2026-09-13T05:50:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-dokument-dokument.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-dokument-dokument.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-13T05:50:21+00:00</t>
+    <t>2026-09-13T06:11:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
